--- a/data/trans_dic/ProbViv_temp-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_temp-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas de temperatura en la vivienda</t>
+          <t>Población con problemas de temperatura, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,42; 52,45</t>
+          <t>43,96; 52,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,67; 52,18</t>
+          <t>46,5; 52,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,55; 51,23</t>
+          <t>46,77; 51,52</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,07; 39,5</t>
+          <t>23,21; 39,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,55; 42,49</t>
+          <t>27,16; 42,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,12; 39,96</t>
+          <t>28,84; 39,95</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,71; 37,89</t>
+          <t>29,83; 37,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,36; 34,68</t>
+          <t>28,35; 34,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,21; 35,29</t>
+          <t>30,1; 35,16</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,56; 39,99</t>
+          <t>28,85; 40,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,61; 42,18</t>
+          <t>31,65; 41,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,78; 40,41</t>
+          <t>32,75; 40,15</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas de temperatura en la vivienda</t>
+          <t>Población con problemas de temperatura, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>228744; 270060</t>
+          <t>226369; 268135</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>352603; 394192</t>
+          <t>351298; 396881</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>591390; 650880</t>
+          <t>594149; 654589</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>551257; 904723</t>
+          <t>531697; 909417</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>594070; 950758</t>
+          <t>607796; 944697</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1273444; 1809573</t>
+          <t>1306049; 1808858</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>192122; 245002</t>
+          <t>192913; 244258</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>187316; 229036</t>
+          <t>187264; 227735</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>394859; 461214</t>
+          <t>393489; 459582</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>985875; 1380419</t>
+          <t>995995; 1380782</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1154960; 1541260</t>
+          <t>1156449; 1528654</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2329273; 2871205</t>
+          <t>2326934; 2852896</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProbViv_temp-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_temp-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>49,55%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>43,96; 52,07</t>
+          <t>44,89; 53,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,5; 52,53</t>
+          <t>47,71; 52,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,77; 51,52</t>
+          <t>47,15; 51,99</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>40,65%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,21; 39,71</t>
+          <t>38,33; 43,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,16; 42,22</t>
+          <t>38,65; 42,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,84; 39,95</t>
+          <t>39,15; 42,27</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,83; 37,77</t>
+          <t>31,03; 38,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,35; 34,48</t>
+          <t>30,05; 36,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,1; 35,16</t>
+          <t>31,52; 36,42</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>41,05%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,85; 40,0</t>
+          <t>39,04; 42,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,65; 41,84</t>
+          <t>39,85; 42,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,75; 40,15</t>
+          <t>39,84; 42,2</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>248274</t>
+          <t>280749</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>373444</t>
+          <t>413184</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>621719</t>
+          <t>693932</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>226369; 268135</t>
+          <t>259696; 307215</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>351298; 396881</t>
+          <t>392175; 434458</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>594149; 654589</t>
+          <t>660351; 728189</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>793831</t>
+          <t>908239</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>819683</t>
+          <t>881260</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1613514</t>
+          <t>1789499</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>531697; 909417</t>
+          <t>854967; 960726</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>607796; 944697</t>
+          <t>839250; 926088</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1306049; 1808858</t>
+          <t>1723374; 1860489</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>219659</t>
+          <t>249525</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>207242</t>
+          <t>242668</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>426901</t>
+          <t>492194</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>192913; 244258</t>
+          <t>220825; 275388</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>187264; 227735</t>
+          <t>220855; 267461</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>393489; 459582</t>
+          <t>455976; 526842</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1261764</t>
+          <t>1438514</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1400370</t>
+          <t>1537112</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2662134</t>
+          <t>2975626</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>995995; 1380782</t>
+          <t>1374591; 1505312</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1156449; 1528654</t>
+          <t>1485815; 1592790</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2326934; 2852896</t>
+          <t>2887875; 3059334</t>
         </is>
       </c>
     </row>
